--- a/XLS-001 - Assumptions, Constraints and Dependencies Register - v0.2.xlsx
+++ b/XLS-001 - Assumptions, Constraints and Dependencies Register - v0.2.xlsx
@@ -486,10 +486,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PMOC Software | Fase 1 | v0.2 DRAFT | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved | Status: aguardando segunda revisão formal da Services.NET | Hipótese NÃO é requisito confirmado.</t>
-        </is>
-      </c>
-    </row>
+          <t>PMOC Software | Fase 1 | v0.2 — APPROVED | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved; Services.NET segunda revisão formal da Fase 1 v0.2 | Status: APPROVED WITH OPEN ACTIONS — Fase 1 aprovada formalmente pela Services.NET em 22/09/2026; Fase 2 não iniciada | Hipótese NÃO é requisito confirmado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -550,17 +551,17 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Existe um cliente-piloto (empresa prestadora de climatização) disponível para validar requisitos e operar o MVP</t>
+          <t>Tenant-piloto identificado como Clima Zero Climatização; interlocutores, disponibilidade para levantamento, compromisso operacional e agenda ainda dependem de formalização</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Alto — sem piloto, requisitos da Fase 2 seriam presumidos</t>
+          <t>Alto — sem disponibilidade operacional e agenda, a Fase 2 produziria requisitos presumidos</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Product Owner (STK-002)</t>
+          <t>Product Owner institucional (STK-002) + Clima Zero Climatização (STK-010)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -575,12 +576,12 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>OQ-010</t>
+          <t>OQ-010, OQ-022, DEP-004</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2 — identidade definida; operação pendente</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1143,7 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Restrições que limitam decisões de produto e arquitetura. | v0.2 DRAFT | 22/09/2026</t>
+          <t>Restrições que limitam decisões de produto e arquitetura. | v0.2 — APPROVED | 22/09/2026</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1481,22 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Cada informação possui uma única fonte autoritativa declarada. Overview_Project.md é REFERENCE / NON-AUTHORITATIVE; a governança M365 × Git após a adoção de edição local/versionamento Git deve ser decidida formalmente em DEC-011</t>
+          <t>Git é a baseline técnica autoritativa e versionada dos artefatos de engenharia formalmente publicados/aprovados. Microsoft 365 é o ambiente de autoria, colaboração, apresentação, visualização executiva, Word, Excel, Power BI e interação com agentes integrados ao ambiente corporativo. Em divergência entre cópia M365 e baseline aprovada no Git, prevalece o Git.</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Master Specification §21; revisão local Codex v0.2</t>
+          <t>DEC-011 aprovada em 22/09/2026; DOC-001 §30</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>v0.2 — status do Overview aplicado; DEC-011 proposta</t>
+          <t>v0.2 — DEC-011 aprovada</t>
         </is>
       </c>
     </row>
@@ -1599,10 +1600,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Dependências externas, de cliente e internas. | v0.2 DRAFT | 22/09/2026</t>
-        </is>
-      </c>
-    </row>
+          <t>Dependências externas, de cliente e internas. | v0.2 — APPROVED | 22/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1764,17 +1766,17 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Disponibilidade do cliente-piloto para levantamento</t>
+          <t>Interlocutores específicos, disponibilidade para levantamento, compromisso operacional e agenda da Clima Zero Climatização</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Product Owner (STK-002)</t>
+          <t>Product Owner institucional (STK-002) + Clima Zero Climatização (STK-010)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Bloqueia Fase 2</t>
+          <t>Bloqueia planejamento operacional da Fase 2 e validação do MVP</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1784,7 +1786,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2 — identidade do tenant definida; operação pendente em OQ-022</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1914,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Designação de patrocinador, Product Owner, autoridade jurídica e DPO</t>
+          <t>Designação de autoridades remanescentes: Jurídico/Regulatório, DPO/Encarregado e responsável técnico operacional. Patrocinador e Product Owner institucional já definidos.</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1922,7 +1924,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Bloqueia aprovação da Fase 1</t>
+          <t>Bloqueia validações jurídica, privacidade e técnica; não bloqueia mais a aprovação formal da Fase 1</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -1932,7 +1934,7 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>v0.2 — inclui Jurídico e DPO</t>
+          <t>v0.2 — patrocinador/PO encerrados; GAP-004 a GAP-006 permanecem</t>
         </is>
       </c>
     </row>
@@ -2051,6 +2053,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="8">
       <c r="A4" s="14" t="inlineStr">
         <is>
